--- a/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
+++ b/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4</v>
+        <v>-0.06586734051805011</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.36</v>
+        <v>-0.04586734051805012</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.3200000000000001</v>
+        <v>-0.02586734051805012</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.28</v>
+        <v>-0.005867340518050115</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.24</v>
+        <v>0.01413265948194989</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.52</v>
+        <v>-0.05086734051805011</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.468</v>
+        <v>-0.03086734051805012</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.416</v>
+        <v>-0.01086734051805012</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.364</v>
+        <v>0.009132659481949884</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.312</v>
+        <v>0.02913265948194989</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.28</v>
+        <v>-0.08086734051805011</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2520000000000001</v>
+        <v>-0.06086734051805012</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.224</v>
+        <v>-0.04086734051805012</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.196</v>
+        <v>-0.02086734051805011</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.168</v>
+        <v>-0.0008673405180501109</v>
       </c>
     </row>
     <row r="11">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6327553031225936</v>
+        <v>0.6227553031225936</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6327553031225936</v>
+        <v>0.6227553031225936</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6327553031225936</v>
+        <v>0.6227553031225936</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.6327553031225936</v>
+        <v>0.6227553031225936</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.6327553031225936</v>
+        <v>0.6227553031225936</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5927553031225936</v>
+        <v>0.6027553031225936</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5927553031225936</v>
+        <v>0.6027553031225936</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5927553031225936</v>
+        <v>0.6027553031225936</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.5927553031225936</v>
+        <v>0.6027553031225936</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.5927553031225936</v>
+        <v>0.6027553031225936</v>
       </c>
     </row>
     <row r="18">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.07574978526865071</v>
+        <v>0.0807497852686507</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.07574978526865071</v>
+        <v>0.0807497852686507</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.07574978526865071</v>
+        <v>0.0807497852686507</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.07574978526865071</v>
+        <v>0.0807497852686507</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.07574978526865071</v>
+        <v>0.0807497852686507</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.0957497852686507</v>
+        <v>0.09074978526865071</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.0957497852686507</v>
+        <v>0.09074978526865071</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.0957497852686507</v>
+        <v>0.09074978526865071</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.0957497852686507</v>
+        <v>0.09074978526865071</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.0957497852686507</v>
+        <v>0.09074978526865071</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.2694068589745261</v>
+        <v>0.2904608565108069</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2694068589745261</v>
+        <v>0.2904608565108069</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.2694068589745261</v>
+        <v>0.2904608565108069</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.2694068589745261</v>
+        <v>0.2904608565108069</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.2694068589745261</v>
+        <v>0.2904608565108069</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0822</v>
+        <v>0.0799</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0722</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1022</v>
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>14.325</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/14.325-1</f>
+        <f>C33/15.54-1</f>
         <v/>
       </c>
     </row>
@@ -3753,176 +3753,176 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0522</v>
+        <v>0.0499</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*7/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*9/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.06219999999999999</v>
+        <v>0.05989999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*7/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*9/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0722</v>
+        <v>0.0699</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*7/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*9/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0822</v>
+        <v>0.0799</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*7/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*9/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.09219999999999999</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*7/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*9/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1022</v>
+        <v>0.0999</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*7/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*9/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1122</v>
+        <v>0.1099</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*7/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*9/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
+++ b/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
@@ -519,7 +519,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc. (WCP.TO) - Assumptions</t>
+          <t>Whitecap Resources Inc. (WCP_TO) - Assumptions</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.08574978526865071</v>
+        <v>0.4136285768837634</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.08574978526865071</v>
+        <v>0.4136285768837634</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.08574978526865071</v>
+        <v>0.4136285768837634</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.08574978526865071</v>
+        <v>0.4136285768837634</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.08574978526865071</v>
+        <v>0.4136285768837634</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0807497852686507</v>
+        <v>0.4086285768837634</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.0807497852686507</v>
+        <v>0.4086285768837634</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.0807497852686507</v>
+        <v>0.4086285768837634</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.0807497852686507</v>
+        <v>0.4086285768837634</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.0807497852686507</v>
+        <v>0.4086285768837634</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.09074978526865071</v>
+        <v>0.4186285768837634</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.09074978526865071</v>
+        <v>0.4186285768837634</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.09074978526865071</v>
+        <v>0.4186285768837634</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.09074978526865071</v>
+        <v>0.4186285768837634</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.09074978526865071</v>
+        <v>0.4186285768837634</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0799</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0699</v>
+        <v>0.0631</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1243,7 +1243,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc. (WCP.TO) - Historical Financial Statements</t>
+          <t>Whitecap Resources Inc. (WCP_TO) - Historical Financial Statements</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -1935,7 +1935,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc. (WCP.TO) - Financial Model</t>
+          <t>Whitecap Resources Inc. (WCP_TO) - Financial Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3255,7 +3255,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc. (WCP.TO) - DCF Valuation</t>
+          <t>Whitecap Resources Inc. (WCP_TO) - DCF Valuation</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>15.54</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/15.54-1</f>
+        <f>C33/15.04-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0499</v>
+        <v>0.0431</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.05989999999999999</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0699</v>
+        <v>0.0631</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0799</v>
+        <v>0.0731</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.0999</v>
+        <v>0.0931</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1099</v>
+        <v>0.1031</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7/(1+$A$45)^5+$C$29)/$C$32</f>

--- a/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
+++ b/data/valuations/WCP_TO/WCP_TO_modelo_valoracion.xlsx
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.06586734051805011</v>
+        <v>0.361</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.04586734051805012</v>
+        <v>0.03</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-0.02586734051805012</v>
+        <v>0.02</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>-0.005867340518050115</v>
+        <v>0.02</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.01413265948194989</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.05086734051805011</v>
+        <v>0.484</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.03086734051805012</v>
+        <v>0.05</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-0.01086734051805012</v>
+        <v>0.04</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.009132659481949884</v>
+        <v>0.03</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.02913265948194989</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.08086734051805011</v>
+        <v>0.262</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.06086734051805012</v>
+        <v>-0.05</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.04086734051805012</v>
+        <v>-0.03</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>-0.02086734051805011</v>
+        <v>-0.02</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>-0.0008673405180501109</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6127553031225936</v>
+        <v>0.58</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.6127553031225936</v>
+        <v>0.58</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.6127553031225936</v>
+        <v>0.58</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.6127553031225936</v>
+        <v>0.58</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.6127553031225936</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.6227553031225936</v>
+        <v>0.62</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6227553031225936</v>
+        <v>0.62</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.6227553031225936</v>
+        <v>0.62</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.6227553031225936</v>
+        <v>0.62</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.6227553031225936</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.6027553031225936</v>
+        <v>0.55</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6027553031225936</v>
+        <v>0.55</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.6027553031225936</v>
+        <v>0.55</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.6027553031225936</v>
+        <v>0.55</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.6027553031225936</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.4136285768837634</v>
+        <v>0.37</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.4136285768837634</v>
+        <v>0.37</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.4136285768837634</v>
+        <v>0.37</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4136285768837634</v>
+        <v>0.37</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.4136285768837634</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.4086285768837634</v>
+        <v>0.35</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.4086285768837634</v>
+        <v>0.35</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4086285768837634</v>
+        <v>0.35</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4086285768837634</v>
+        <v>0.35</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.4086285768837634</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.4186285768837634</v>
+        <v>0.38</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.4186285768837634</v>
+        <v>0.38</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4186285768837634</v>
+        <v>0.38</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4186285768837634</v>
+        <v>0.38</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.4186285768837634</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2326065773325618</v>
+        <v>0.33</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2326065773325618</v>
+        <v>0.33</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2326065773325618</v>
+        <v>0.33</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.2326065773325618</v>
+        <v>0.33</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.2326065773325618</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.2904608565108069</v>
+        <v>0.3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.2904608565108069</v>
+        <v>0.3</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.2904608565108069</v>
+        <v>0.3</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.2904608565108069</v>
+        <v>0.3</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.2904608565108069</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.2879027752612194</v>
+        <v>0.25</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.2879027752612194</v>
+        <v>0.25</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.2879027752612194</v>
+        <v>0.25</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.2879027752612194</v>
+        <v>0.25</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.2879027752612194</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.0731</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0631</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>15.04</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/15.04-1</f>
+        <f>C33/14.43-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>7x</t>
+          <t>2x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>9x</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>11x</t>
+          <t>6x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>13x</t>
+          <t>8x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>10x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0431</v>
+        <v>0.075</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*1.5/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*3.5/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*5.5/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*7.5/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*9.5/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*1.5/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*3.5/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*5.5/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*7.5/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*9.5/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0631</v>
+        <v>0.095</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*1.5/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*3.5/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*5.5/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*7.5/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*9.5/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.0731</v>
+        <v>0.105</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*1.5/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*3.5/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*5.5/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*7.5/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*9.5/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*1.5/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*3.5/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*5.5/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*7.5/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*9.5/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.0931</v>
+        <v>0.125</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*1.5/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*3.5/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*5.5/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*7.5/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*9.5/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1031</v>
+        <v>0.135</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*1.5/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*3.5/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*5.5/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*7.5/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*9.5/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
